--- a/tests/fixtures/ideal_input/deals.xlsx
+++ b/tests/fixtures/ideal_input/deals.xlsx
@@ -509,37 +509,37 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>basis</t>
+          <t>pay_receive</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>indexation</t>
+          <t>notional</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>instrument_type</t>
+          <t>last_fixing_date</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>pay_receive</t>
+          <t>next_fixing_date</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>notional</t>
+          <t>hedge_type</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>last_fixing_date</t>
+          <t>ias_standard</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>next_fixing_date</t>
+          <t>designation_date</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,11 @@
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>STRAT_CHF_001</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>CC</t>
@@ -612,21 +616,25 @@
           <t>THCCBFIGE</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Act/360</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>IFRS9</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -697,17 +705,9 @@
           <t>BKCCBFIGE</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Act/360</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
@@ -771,7 +771,11 @@
           <t>2027-06-12</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>STRAT_CHF_002</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>CC</t>
@@ -782,21 +786,25 @@
           <t>THCCBFIGE</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Act/360</t>
-        </is>
-      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Loan</t>
-        </is>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>fair_value</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>IAS39</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -871,17 +879,9 @@
           <t>WCCCBFIGE</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Act/360</t>
-        </is>
-      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Loan</t>
-        </is>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -956,17 +956,9 @@
           <t>THCCHFIGE</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>30/360</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Bond</t>
-        </is>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
@@ -1030,7 +1022,11 @@
           <t>2030-06-17</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>STRAT_EUR_001</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>CC</t>
@@ -1041,21 +1037,25 @@
           <t>BKCCBFIGE</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>30/360</t>
-        </is>
-      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Bond</t>
-        </is>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>IFRS9</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1126,17 +1126,9 @@
           <t>CLI-MT-CIB</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Act/360</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>FX Swap</t>
-        </is>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
@@ -1211,17 +1203,9 @@
           <t>THCCBFIGE</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Act/365</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -1285,11 +1269,7 @@
           <t>2028-02-03</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>STRAT_001</t>
-        </is>
-      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>CC</t>
@@ -1300,17 +1280,9 @@
           <t>THCCBFIGE</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Act/360</t>
-        </is>
-      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -1385,17 +1357,9 @@
           <t>THCCBFIGE</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Act/360</t>
-        </is>
-      </c>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
@@ -1463,7 +1427,11 @@
           <t>2030-03-17</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>STRAT_CHF_001</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>CC</t>
@@ -1476,31 +1444,35 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Act/360</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>100000000</v>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>PAY</t>
-        </is>
-      </c>
-      <c r="W12" t="n">
-        <v>100000000</v>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>IFRS9</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-06-15</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1538,11 @@
           <t>2029-11-03</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>STRAT_CHF_002</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>CC</t>
@@ -1579,31 +1555,35 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Act/360</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>RECEIVE</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>75000000</v>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>RECEIVE</t>
-        </is>
-      </c>
-      <c r="W13" t="n">
-        <v>75000000</v>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>fair_value</t>
+        </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>IAS39</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2025-01-20</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1649,11 @@
           <t>2028-06-03</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>STRAT_EUR_001</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>CC</t>
@@ -1682,31 +1666,35 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Act/360</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>50000000</v>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>PAY</t>
-        </is>
-      </c>
-      <c r="W14" t="n">
-        <v>50000000</v>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>IFRS9</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-09-01</t>
         </is>
       </c>
     </row>

--- a/tests/fixtures/ideal_input/deals.xlsx
+++ b/tests/fixtures/ideal_input/deals.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y14"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,37 +509,42 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>hedge_type</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ias_standard</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>designation_date</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>pay_receive</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>notional</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>last_fixing_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>next_fixing_date</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>hedge_type</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>ias_standard</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>designation_date</t>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>current_fixing_rate</t>
         </is>
       </c>
     </row>
@@ -616,25 +621,26 @@
           <t>THCCBFIGE</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>IFRS9</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>IFRS9</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -712,6 +718,7 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -786,25 +793,26 @@
           <t>THCCBFIGE</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>fair_value</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>IAS39</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>fair_value</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>IAS39</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-01-20</t>
-        </is>
-      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -874,11 +882,7 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>WCCCBFIGE</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -886,6 +890,7 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -951,11 +956,7 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>THCCHFIGE</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -963,6 +964,7 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1037,25 +1039,26 @@
           <t>BKCCBFIGE</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>IFRS9</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>IFRS9</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1121,11 +1124,7 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>CLI-MT-CIB</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1133,6 +1132,7 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1198,11 +1198,7 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>THCCBFIGE</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -1210,6 +1206,7 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1287,6 +1284,7 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1364,14 +1362,15 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>400001</v>
+        <v>100008</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>IAM/LD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1381,57 +1380,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BOOK2</t>
+          <t>BOOK1</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-40000000</v>
       </c>
       <c r="G12" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>SARON</t>
+          <t>SARON3M</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2030-03-17</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>STRAT_CHF_001</t>
-        </is>
-      </c>
+          <t>2029-01-17</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
           <t>CC</t>
@@ -1442,52 +1437,37 @@
           <t>THCCBFIGE</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>PAY</t>
-        </is>
-      </c>
-      <c r="T12" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>IFRS9</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.008500000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>400002</v>
+        <v>100009</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IRS</t>
+          <t>IAM/LD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1497,52 +1477,48 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BOOK2</t>
+          <t>BOOK1</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0095</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.0235</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>SARON</t>
+          <t>ESTR6M</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2029-11-03</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>STRAT_CHF_002</t>
-        </is>
-      </c>
+          <t>2028-10-09</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
           <t>CC</t>
@@ -1553,149 +1529,365 @@
           <t>BKCCBFIGE</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>RECEIVE</t>
-        </is>
-      </c>
-      <c r="T13" t="n">
-        <v>75000000</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>fair_value</t>
-        </is>
-      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
-          <t>IAS39</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
-        </is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.021</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>400001</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IRS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BOOK2</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>SARON</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2030-03-17</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>STRAT_CHF_001</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>THCCBFIGE</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>IFRS9</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.0078</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>400002</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IRS</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BOOK2</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>SARON</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2029-11-03</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>STRAT_CHF_002</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>CC</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>BKCCBFIGE</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>fair_value</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>IAS39</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2025-01-20</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>RECEIVE</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.008200000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>400003</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>IRS</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>BOOK2</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.023</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>ESTR</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>2025-06-01</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>2025-06-03</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>2028-06-03</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>STRAT_EUR_001</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>CC</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>CLI-MT-CIB</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>IFRS9</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>PAY</t>
         </is>
       </c>
-      <c r="T14" t="n">
+      <c r="W16" t="n">
         <v>50000000</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>IFRS9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
+      <c r="Z16" t="n">
+        <v>0.022</v>
       </c>
     </row>
   </sheetData>
